--- a/data/trans_dic/P56$pareja-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P56$pareja-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,17; 57,44</t>
+          <t>13,34; 58,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,78; 89,95</t>
+          <t>29,63; 89,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,59; 78,26</t>
+          <t>37,04; 78,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,25; 31,74</t>
+          <t>7,98; 32,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,35</t>
+          <t>0,0; 38,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,41; 43,39</t>
+          <t>13,98; 43,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,19; 33,04</t>
+          <t>7,54; 33,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,87; 19,13</t>
+          <t>7,83; 18,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,74; 35,92</t>
+          <t>9,0; 38,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,25; 48,39</t>
+          <t>21,33; 47,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,39; 42,98</t>
+          <t>19,05; 42,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,65; 19,7</t>
+          <t>9,66; 19,94</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,32; 79,8</t>
+          <t>32,54; 79,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,47; 52,76</t>
+          <t>17,08; 55,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,9; 51,23</t>
+          <t>8,93; 48,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,89; 42,57</t>
+          <t>14,04; 43,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 42,0</t>
+          <t>7,28; 39,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 19,83</t>
+          <t>3,37; 19,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 31,57</t>
+          <t>5,1; 33,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,29; 27,56</t>
+          <t>14,7; 28,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,06; 49,12</t>
+          <t>19,64; 48,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 27,25</t>
+          <t>10,82; 27,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 33,13</t>
+          <t>9,34; 33,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,78; 29,12</t>
+          <t>16,82; 29,34</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,78; 75,13</t>
+          <t>11,04; 76,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,7; 77,31</t>
+          <t>16,55; 77,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,54; 70,97</t>
+          <t>21,19; 71,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34,18; 71,74</t>
+          <t>32,74; 69,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,2</t>
+          <t>0,0; 26,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 26,34</t>
+          <t>5,11; 26,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 32,94</t>
+          <t>5,73; 33,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 21,43</t>
+          <t>6,08; 20,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 35,56</t>
+          <t>5,84; 32,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,36; 36,29</t>
+          <t>11,04; 35,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,85; 41,35</t>
+          <t>15,2; 40,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,28; 34,47</t>
+          <t>17,14; 34,1</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,54; 63,01</t>
+          <t>18,59; 62,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,57; 72,44</t>
+          <t>23,22; 71,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,77; 82,8</t>
+          <t>32,29; 80,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,87; 61,01</t>
+          <t>33,34; 61,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,19</t>
+          <t>0,0; 20,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 21,62</t>
+          <t>3,89; 20,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 24,21</t>
+          <t>2,36; 25,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,2; 19,22</t>
+          <t>7,73; 19,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 26,87</t>
+          <t>7,13; 26,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,75; 33,24</t>
+          <t>11,34; 33,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,03; 35,36</t>
+          <t>12,32; 34,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,05; 28,9</t>
+          <t>17,05; 29,47</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,42; 56,12</t>
+          <t>30,1; 57,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,3; 55,11</t>
+          <t>30,14; 55,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,82; 59,55</t>
+          <t>35,47; 57,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,63; 44,67</t>
+          <t>29,15; 43,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 19,31</t>
+          <t>5,82; 19,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,84; 20,17</t>
+          <t>9,93; 20,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,65; 20,57</t>
+          <t>8,57; 20,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,01; 17,96</t>
+          <t>11,77; 18,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,67; 28,44</t>
+          <t>15,68; 28,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,51; 28,33</t>
+          <t>17,62; 28,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,6; 30,21</t>
+          <t>18,37; 29,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,78; 24,13</t>
+          <t>17,54; 24,11</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>938; 7519</t>
+          <t>1747; 7702</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3153; 9524</t>
+          <t>3137; 9523</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7322; 14848</t>
+          <t>7027; 14849</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2069; 7965</t>
+          <t>2004; 8172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6613</t>
+          <t>0; 6385</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7566; 20007</t>
+          <t>6445; 20282</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3263; 13155</t>
+          <t>3002; 13297</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4870; 11833</t>
+          <t>4840; 11637</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2576; 10588</t>
+          <t>2654; 11485</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12052; 27437</t>
+          <t>12093; 26720</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11986; 25267</t>
+          <t>11199; 24821</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8394; 17124</t>
+          <t>8402; 17336</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4838; 11943</t>
+          <t>4871; 11915</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5336; 17091</t>
+          <t>5534; 17984</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1736; 9990</t>
+          <t>1741; 9476</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3638; 10398</t>
+          <t>3430; 10507</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2041; 11495</t>
+          <t>1992; 10762</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2990; 13020</t>
+          <t>2213; 12887</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2011; 12966</t>
+          <t>2093; 13578</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9563; 18442</t>
+          <t>9838; 19082</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8495; 20795</t>
+          <t>8315; 20660</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10645; 26725</t>
+          <t>10607; 26901</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5234; 20066</t>
+          <t>5660; 20420</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15330; 26602</t>
+          <t>15359; 26798</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>749; 5225</t>
+          <t>768; 5312</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2474; 10804</t>
+          <t>2313; 10865</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4138; 12476</t>
+          <t>3726; 12495</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6938; 14562</t>
+          <t>6646; 14186</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4800</t>
+          <t>0; 4660</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2118; 11113</t>
+          <t>2156; 11282</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1986; 11543</t>
+          <t>2008; 11676</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2550; 9048</t>
+          <t>2567; 8743</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1506; 8747</t>
+          <t>1436; 8079</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6379; 20382</t>
+          <t>6203; 19696</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8342; 21763</t>
+          <t>7998; 21421</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10180; 21551</t>
+          <t>10713; 21317</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2459; 8360</t>
+          <t>2466; 8324</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5078; 15607</t>
+          <t>5002; 15479</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5579; 13286</t>
+          <t>5181; 12992</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10921; 19671</t>
+          <t>10751; 19688</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5525</t>
+          <t>0; 6497</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1985; 11084</t>
+          <t>1994; 10551</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1282; 13520</t>
+          <t>1320; 14318</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6563; 15386</t>
+          <t>6188; 15557</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3315; 12201</t>
+          <t>3239; 12147</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8557; 24205</t>
+          <t>8255; 24201</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9367; 25423</t>
+          <t>8859; 24642</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19143; 32456</t>
+          <t>19148; 33090</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13721; 27095</t>
+          <t>14530; 27529</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23790; 43266</t>
+          <t>23659; 43177</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26543; 42937</t>
+          <t>25572; 41326</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29216; 45587</t>
+          <t>29755; 44707</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5814; 18067</t>
+          <t>5442; 17941</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20190; 41405</t>
+          <t>20387; 42514</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14854; 35333</t>
+          <t>14730; 35472</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30139; 45077</t>
+          <t>29544; 46061</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22230; 40330</t>
+          <t>22241; 41080</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49691; 80387</t>
+          <t>49996; 79773</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45362; 73683</t>
+          <t>44807; 72443</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>62793; 85196</t>
+          <t>61941; 85141</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$pareja-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P56$pareja-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,34; 58,83</t>
+          <t>8,3; 64,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,63; 89,94</t>
+          <t>29,55; 90,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,04; 78,26</t>
+          <t>38,57; 78,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,98; 32,56</t>
+          <t>9,08; 33,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,96</t>
+          <t>0,0; 39,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,98; 43,98</t>
+          <t>15,29; 42,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,54; 33,39</t>
+          <t>7,56; 32,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,83; 18,82</t>
+          <t>7,93; 19,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,0; 38,96</t>
+          <t>8,92; 36,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,33; 47,12</t>
+          <t>22,38; 47,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,05; 42,22</t>
+          <t>19,64; 43,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,66; 19,94</t>
+          <t>9,38; 19,29</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,54; 79,61</t>
+          <t>32,0; 85,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,08; 55,51</t>
+          <t>16,82; 52,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,93; 48,6</t>
+          <t>8,93; 46,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,04; 43,02</t>
+          <t>16,27; 44,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,28; 39,32</t>
+          <t>7,58; 39,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 19,63</t>
+          <t>4,74; 19,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,1; 33,06</t>
+          <t>4,95; 32,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,7; 28,52</t>
+          <t>15,16; 29,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,64; 48,8</t>
+          <t>19,94; 50,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,82; 27,43</t>
+          <t>10,18; 26,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 33,72</t>
+          <t>8,69; 34,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,82; 29,34</t>
+          <t>17,42; 30,63</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,04; 76,37</t>
+          <t>10,67; 76,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,55; 77,74</t>
+          <t>16,91; 77,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,19; 71,08</t>
+          <t>22,61; 70,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32,74; 69,89</t>
+          <t>33,13; 69,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,41</t>
+          <t>0,0; 27,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 26,74</t>
+          <t>4,86; 25,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 33,32</t>
+          <t>5,72; 30,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,08; 20,71</t>
+          <t>6,31; 21,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 32,84</t>
+          <t>6,16; 35,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,04; 35,06</t>
+          <t>11,41; 35,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,2; 40,7</t>
+          <t>14,93; 40,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,14; 34,1</t>
+          <t>17,31; 34,58</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,59; 62,74</t>
+          <t>12,84; 62,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,22; 71,84</t>
+          <t>24,85; 73,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,29; 80,97</t>
+          <t>32,21; 79,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,34; 61,06</t>
+          <t>35,07; 62,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,21</t>
+          <t>0,0; 17,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 20,58</t>
+          <t>3,85; 20,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 25,63</t>
+          <t>3,04; 22,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,73; 19,43</t>
+          <t>8,17; 18,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,13; 26,75</t>
+          <t>6,95; 26,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,34; 33,24</t>
+          <t>11,43; 32,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,32; 34,27</t>
+          <t>11,72; 32,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,05; 29,47</t>
+          <t>16,96; 28,75</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,1; 57,02</t>
+          <t>27,88; 54,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,14; 55,0</t>
+          <t>30,44; 55,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,47; 57,32</t>
+          <t>37,16; 59,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,15; 43,81</t>
+          <t>29,36; 44,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 19,18</t>
+          <t>6,24; 20,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,93; 20,71</t>
+          <t>9,99; 20,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,57; 20,65</t>
+          <t>8,91; 20,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,77; 18,35</t>
+          <t>11,92; 18,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,68; 28,97</t>
+          <t>16,13; 29,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,62; 28,11</t>
+          <t>16,66; 27,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,37; 29,7</t>
+          <t>18,48; 29,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,54; 24,11</t>
+          <t>18,01; 24,42</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12812</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1747; 7702</t>
+          <t>1087; 8447</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3137; 9523</t>
+          <t>3129; 9533</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7027; 14849</t>
+          <t>7317; 14872</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2004; 8172</t>
+          <t>2369; 8712</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6385</t>
+          <t>0; 6433</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6445; 20282</t>
+          <t>7053; 19588</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3002; 13297</t>
+          <t>3009; 12756</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4840; 11637</t>
+          <t>5219; 12529</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2654; 11485</t>
+          <t>2631; 10853</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12093; 26720</t>
+          <t>12690; 26879</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11199; 24821</t>
+          <t>11549; 25462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8402; 17336</t>
+          <t>8615; 17724</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>16263</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>23580</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4871; 11915</t>
+          <t>4790; 12827</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5534; 17984</t>
+          <t>5451; 17149</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1741; 9476</t>
+          <t>1742; 9102</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3430; 10507</t>
+          <t>4272; 11690</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1992; 10762</t>
+          <t>2074; 10709</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2213; 12887</t>
+          <t>3112; 13118</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2093; 13578</t>
+          <t>2034; 13355</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9838; 19082</t>
+          <t>11227; 21604</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8315; 20660</t>
+          <t>8444; 21335</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10607; 26901</t>
+          <t>9978; 26102</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5660; 20420</t>
+          <t>5261; 20747</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15359; 26798</t>
+          <t>17468; 30721</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15493</t>
+          <t>17804</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>768; 5312</t>
+          <t>742; 5305</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2313; 10865</t>
+          <t>2363; 10839</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3726; 12495</t>
+          <t>3974; 12447</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6646; 14186</t>
+          <t>7660; 16174</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4660</t>
+          <t>0; 4811</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2156; 11282</t>
+          <t>2049; 10784</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2008; 11676</t>
+          <t>2006; 10837</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2567; 8743</t>
+          <t>3010; 10059</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1436; 8079</t>
+          <t>1516; 8775</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6203; 19696</t>
+          <t>6407; 20011</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7998; 21421</t>
+          <t>7855; 21498</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10713; 21317</t>
+          <t>12256; 24488</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>15858</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>26888</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2466; 8324</t>
+          <t>1703; 8340</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5002; 15479</t>
+          <t>5354; 15734</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5181; 12992</t>
+          <t>5168; 12720</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10751; 19688</t>
+          <t>11614; 20824</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6497</t>
+          <t>0; 5632</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1994; 10551</t>
+          <t>1975; 10407</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1320; 14318</t>
+          <t>1699; 12782</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6188; 15557</t>
+          <t>7178; 16273</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3239; 12147</t>
+          <t>3154; 12067</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8255; 24201</t>
+          <t>8327; 23398</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8859; 24642</t>
+          <t>8430; 23408</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19148; 33090</t>
+          <t>20526; 34785</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36720</t>
+          <t>39743</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36915</t>
+          <t>41340</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73635</t>
+          <t>81083</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14530; 27529</t>
+          <t>13462; 26214</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23659; 43177</t>
+          <t>23900; 43723</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25572; 41326</t>
+          <t>26789; 43080</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29755; 44707</t>
+          <t>31882; 48288</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5442; 17941</t>
+          <t>5841; 19438</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20387; 42514</t>
+          <t>20512; 41476</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14730; 35472</t>
+          <t>15306; 35917</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29544; 46061</t>
+          <t>32831; 50323</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22241; 41080</t>
+          <t>22875; 42002</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49996; 79773</t>
+          <t>47261; 78376</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44807; 72443</t>
+          <t>45064; 73099</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>61941; 85141</t>
+          <t>69153; 93755</t>
         </is>
       </c>
     </row>
